--- a/GSA SQA_Test_Cases.xlsx
+++ b/GSA SQA_Test_Cases.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="102">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -92,12 +92,6 @@
     <t>TC-06</t>
   </si>
   <si>
-    <t>Create assignment with empty fields</t>
-  </si>
-  <si>
-    <t>Submit without filling fields</t>
-  </si>
-  <si>
     <t>Validation error</t>
   </si>
   <si>
@@ -249,9 +243,6 @@
   </si>
   <si>
     <t>Redirect to login</t>
-  </si>
-  <si>
-    <t>TC-20</t>
   </si>
   <si>
     <t>API access without JWT</t>
@@ -666,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -683,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" t="s">
         <v>82</v>
-      </c>
-      <c r="C1" t="s">
-        <v>85</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -701,7 +692,7 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -709,7 +700,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -724,7 +715,7 @@
         <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -732,7 +723,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -747,7 +738,7 @@
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -755,7 +746,7 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
@@ -770,7 +761,7 @@
         <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -778,7 +769,7 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -793,7 +784,7 @@
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -801,7 +792,7 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
@@ -816,7 +807,7 @@
         <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -824,254 +815,246 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="G8" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="G9" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" t="s">
         <v>37</v>
       </c>
-      <c r="D10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" t="s">
-        <v>39</v>
-      </c>
       <c r="G10" t="s">
-        <v>86</v>
+        <v>101</v>
+      </c>
+      <c r="H10" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H11" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
         <v>78</v>
-      </c>
-      <c r="C21" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" t="s">
-        <v>80</v>
-      </c>
-      <c r="E21" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1098,16 +1081,16 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" t="s">
         <v>87</v>
-      </c>
-      <c r="B1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D1" t="s">
-        <v>90</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -1116,48 +1099,48 @@
         <v>3</v>
       </c>
       <c r="G1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I1" t="s">
         <v>4</v>
       </c>
       <c r="J1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" t="s">
         <v>94</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>95</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>96</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>97</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>98</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>99</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
         <v>100</v>
-      </c>
-      <c r="H2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I2" t="s">
-        <v>102</v>
-      </c>
-      <c r="J2" t="s">
-        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/GSA SQA_Test_Cases.xlsx
+++ b/GSA SQA_Test_Cases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="555" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="390" yWindow="555" windowWidth="19815" windowHeight="9405" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="102">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -212,48 +212,12 @@
     <t>Status = completed</t>
   </si>
   <si>
-    <t>TC-17</t>
-  </si>
-  <si>
     <t>Give mark without input</t>
   </si>
   <si>
     <t>Submit empty mark</t>
   </si>
   <si>
-    <t>TC-18</t>
-  </si>
-  <si>
-    <t>Status change after marking</t>
-  </si>
-  <si>
-    <t>Mark assignment</t>
-  </si>
-  <si>
-    <t>Pending → Completed</t>
-  </si>
-  <si>
-    <t>TC-19</t>
-  </si>
-  <si>
-    <t>Access private route without login</t>
-  </si>
-  <si>
-    <t>Open private route</t>
-  </si>
-  <si>
-    <t>Redirect to login</t>
-  </si>
-  <si>
-    <t>API access without JWT</t>
-  </si>
-  <si>
-    <t>Call API without token</t>
-  </si>
-  <si>
-    <t>Unauthorized (401)</t>
-  </si>
-  <si>
     <t>Module</t>
   </si>
   <si>
@@ -321,16 +285,59 @@
   </si>
   <si>
     <t>Failled</t>
+  </si>
+  <si>
+    <t>Validation is not error</t>
+  </si>
+  <si>
+    <t>BUG-Submit -02</t>
+  </si>
+  <si>
+    <t>According to the requirement, Submit empty Solution then Show Validation error. However, the system allows empty Solution.</t>
+  </si>
+  <si>
+    <t>A user will take a specific assignment, then fill out the form, then submit it.</t>
+  </si>
+  <si>
+    <t>BUG-Mark -03</t>
+  </si>
+  <si>
+    <t>Give mark The Assignment</t>
+  </si>
+  <si>
+    <t>According to the requirement, Give Mark and Show Status = completed. However, the system Show Status = Pending</t>
+  </si>
+  <si>
+    <t>A user will take a specific assignment and then mark it.</t>
+  </si>
+  <si>
+    <t>Status = Pending</t>
+  </si>
+  <si>
+    <t>BUG-Mark -04</t>
+  </si>
+  <si>
+    <t>Give Without Mark</t>
+  </si>
+  <si>
+    <t>According to the requirement, Give without mark then Show Validation error. However, the system allows empty Mark.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -356,8 +363,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -657,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -667,6 +677,7 @@
     <col min="5" max="5" width="31.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -674,10 +685,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -692,7 +703,7 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -700,7 +711,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -715,7 +726,7 @@
         <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -723,7 +734,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -738,7 +749,7 @@
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -746,7 +757,7 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
@@ -761,7 +772,7 @@
         <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -769,7 +780,7 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -784,7 +795,7 @@
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -792,7 +803,7 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
@@ -807,7 +818,7 @@
         <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -815,7 +826,7 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
@@ -830,7 +841,7 @@
         <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -838,7 +849,7 @@
         <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
         <v>31</v>
@@ -853,7 +864,7 @@
         <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -861,7 +872,7 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
         <v>35</v>
@@ -876,7 +887,7 @@
         <v>37</v>
       </c>
       <c r="G9" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -884,7 +895,7 @@
         <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
         <v>39</v>
@@ -899,10 +910,10 @@
         <v>37</v>
       </c>
       <c r="G10" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="H10" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -910,7 +921,7 @@
         <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
         <v>43</v>
@@ -925,7 +936,7 @@
         <v>45</v>
       </c>
       <c r="G11" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -933,7 +944,7 @@
         <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
         <v>47</v>
@@ -949,6 +960,9 @@
       <c r="A13" t="s">
         <v>46</v>
       </c>
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
       <c r="C13" t="s">
         <v>51</v>
       </c>
@@ -957,12 +971,21 @@
       </c>
       <c r="E13" t="s">
         <v>53</v>
+      </c>
+      <c r="F13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>50</v>
       </c>
+      <c r="B14" t="s">
+        <v>69</v>
+      </c>
       <c r="C14" t="s">
         <v>55</v>
       </c>
@@ -971,12 +994,24 @@
       </c>
       <c r="E14" t="s">
         <v>25</v>
+      </c>
+      <c r="F14" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>54</v>
       </c>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
       <c r="C15" t="s">
         <v>58</v>
       </c>
@@ -985,12 +1020,21 @@
       </c>
       <c r="E15" t="s">
         <v>60</v>
+      </c>
+      <c r="F15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>57</v>
       </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
       <c r="C16" t="s">
         <v>62</v>
       </c>
@@ -1000,61 +1044,40 @@
       <c r="E16" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>61</v>
       </c>
+      <c r="B17" t="s">
+        <v>69</v>
+      </c>
       <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
         <v>66</v>
-      </c>
-      <c r="D17" t="s">
-        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20" t="s">
-        <v>78</v>
+      <c r="F17" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1064,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
@@ -1081,16 +1104,16 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -1099,51 +1122,148 @@
         <v>3</v>
       </c>
       <c r="G1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="H1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I1" t="s">
         <v>4</v>
       </c>
       <c r="J1" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>91</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D3" t="s">
         <v>93</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>94</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B4" t="s">
         <v>95</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C4" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G2" t="s">
+      <c r="D4" t="s">
         <v>97</v>
       </c>
-      <c r="H2" t="s">
+      <c r="E4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" t="s">
         <v>98</v>
       </c>
-      <c r="I2" t="s">
+      <c r="G4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>99</v>
       </c>
-      <c r="J2" t="s">
+      <c r="B5" t="s">
         <v>100</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>